--- a/data/availability/projects/nations-of-sky/jirian-nations-of-sky.xlsx
+++ b/data/availability/projects/nations-of-sky/jirian-nations-of-sky.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
